--- a/03_Group_comparisons/Proteome/05_Classification/03_Modules/c_data/module_classification_all_inputs.xlsx
+++ b/03_Group_comparisons/Proteome/05_Classification/03_Modules/c_data/module_classification_all_inputs.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2691" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2736" uniqueCount="258">
   <si>
     <t>sheet</t>
   </si>
@@ -312,34 +312,34 @@
     <t>greenyellow</t>
   </si>
   <si>
-    <t>03_Cluster_groups/Proteome/06_Classification/03_Modules/T1/c_data/module_classification.xlsx</t>
-  </si>
-  <si>
-    <t>b55d1482a78613274b3520461b9b0430</t>
-  </si>
-  <si>
-    <t>03_Cluster_groups/Proteome/06_Classification/03_Modules/T2/c_data/module_classification.xlsx</t>
-  </si>
-  <si>
-    <t>7e630aa410c2e6e0ce0155fd434fd3f7</t>
-  </si>
-  <si>
-    <t>03_Cluster_groups/Proteome/06_Classification/03_Modules/T3/c_data/module_classification.xlsx</t>
-  </si>
-  <si>
-    <t>43a2d8c768466f43a882d7af290d4328</t>
-  </si>
-  <si>
-    <t>03_Cluster_groups/Proteome/06_Classification/03_Modules/training/c_data/module_classification.xlsx</t>
-  </si>
-  <si>
-    <t>fa3149cdc9c4775d4ba86853915621d3</t>
-  </si>
-  <si>
-    <t>03_Cluster_groups/Proteome/06_Classification/03_Modules/acute/c_data/module_classification.xlsx</t>
-  </si>
-  <si>
-    <t>3b5b76802402d90ef07081fd9c936c35</t>
+    <t>03_Group_comparisons/Proteome/05_Classification/03_Modules/T1/c_data/module_classification.xlsx</t>
+  </si>
+  <si>
+    <t>7dcc6aad3d9589279a7edd748b8e30dd</t>
+  </si>
+  <si>
+    <t>03_Group_comparisons/Proteome/05_Classification/03_Modules/T2/c_data/module_classification.xlsx</t>
+  </si>
+  <si>
+    <t>4a846b61169b71c1d54ac4673726b5f7</t>
+  </si>
+  <si>
+    <t>03_Group_comparisons/Proteome/05_Classification/03_Modules/T3/c_data/module_classification.xlsx</t>
+  </si>
+  <si>
+    <t>f97d3d53ea3e70223c5f0628b7cdb2c1</t>
+  </si>
+  <si>
+    <t>03_Group_comparisons/Proteome/05_Classification/03_Modules/training/c_data/module_classification.xlsx</t>
+  </si>
+  <si>
+    <t>6598fbc28466dfc782f2a0c55d7a6953</t>
+  </si>
+  <si>
+    <t>03_Group_comparisons/Proteome/05_Classification/03_Modules/acute/c_data/module_classification.xlsx</t>
+  </si>
+  <si>
+    <t>78e870bed98446380fe7c25a0518072d</t>
   </si>
   <si>
     <t>BiocGenerics</t>
@@ -444,12 +444,33 @@
     <t>1.2.1</t>
   </si>
   <si>
+    <t>enrichVolcano</t>
+  </si>
+  <si>
+    <t>0.3.0.9000</t>
+  </si>
+  <si>
+    <t>Github (Dustyn-T-Lewis/enrichVolcano@d3fed631f4ae95e01bd61137699313f8de5cc86e)</t>
+  </si>
+  <si>
+    <t>evaluate</t>
+  </si>
+  <si>
+    <t>1.0.5</t>
+  </si>
+  <si>
     <t>farver</t>
   </si>
   <si>
     <t>2.1.2</t>
   </si>
   <si>
+    <t>fastmap</t>
+  </si>
+  <si>
+    <t>1.2.0</t>
+  </si>
+  <si>
     <t>foreach</t>
   </si>
   <si>
@@ -501,6 +522,18 @@
     <t>1.1.4</t>
   </si>
   <si>
+    <t>htmltools</t>
+  </si>
+  <si>
+    <t>0.5.9</t>
+  </si>
+  <si>
+    <t>htmlwidgets</t>
+  </si>
+  <si>
+    <t>1.6.4</t>
+  </si>
+  <si>
     <t>IRanges</t>
   </si>
   <si>
@@ -513,6 +546,18 @@
     <t>1.0.14</t>
   </si>
   <si>
+    <t>jsonlite</t>
+  </si>
+  <si>
+    <t>2.0.0</t>
+  </si>
+  <si>
+    <t>knitr</t>
+  </si>
+  <si>
+    <t>1.51</t>
+  </si>
+  <si>
     <t>labeling</t>
   </si>
   <si>
@@ -522,9 +567,6 @@
     <t>lifecycle</t>
   </si>
   <si>
-    <t>1.0.5</t>
-  </si>
-  <si>
     <t>magrittr</t>
   </si>
   <si>
@@ -537,6 +579,12 @@
     <t>1.5.0</t>
   </si>
   <si>
+    <t>otel</t>
+  </si>
+  <si>
+    <t>0.2.0</t>
+  </si>
+  <si>
     <t>pillar</t>
   </si>
   <si>
@@ -549,6 +597,12 @@
     <t>2.0.3</t>
   </si>
   <si>
+    <t>plyr</t>
+  </si>
+  <si>
+    <t>1.8.9</t>
+  </si>
+  <si>
     <t>png</t>
   </si>
   <si>
@@ -570,6 +624,9 @@
     <t>1.2.2</t>
   </si>
   <si>
+    <t>2.44.0</t>
+  </si>
+  <si>
     <t>R6</t>
   </si>
   <si>
@@ -606,6 +663,9 @@
     <t>1.2.3</t>
   </si>
   <si>
+    <t>reshape2</t>
+  </si>
+  <si>
     <t>rjson</t>
   </si>
   <si>
@@ -618,6 +678,12 @@
     <t>1.3.0</t>
   </si>
   <si>
+    <t>rmarkdown</t>
+  </si>
+  <si>
+    <t>2.31</t>
+  </si>
+  <si>
     <t>rprojroot</t>
   </si>
   <si>
@@ -687,6 +753,12 @@
     <t>0.5.0</t>
   </si>
   <si>
+    <t>utf8</t>
+  </si>
+  <si>
+    <t>1.2.6</t>
+  </si>
+  <si>
     <t>vctrs</t>
   </si>
   <si>
@@ -709,6 +781,18 @@
   </si>
   <si>
     <t>2.0.1</t>
+  </si>
+  <si>
+    <t>xfun</t>
+  </si>
+  <si>
+    <t>0.57</t>
+  </si>
+  <si>
+    <t>yaml</t>
+  </si>
+  <si>
+    <t>2.3.12</t>
   </si>
 </sst>
 </file>
@@ -19254,7 +19338,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C62"/>
+  <dimension ref="A1:C77"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
@@ -19452,15 +19536,15 @@
         <v>142</v>
       </c>
       <c r="C18" t="s">
-        <v>112</v>
+        <v>143</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B19" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C19" t="s">
         <v>112</v>
@@ -19468,10 +19552,10 @@
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B20" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C20" t="s">
         <v>112</v>
@@ -19479,10 +19563,10 @@
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B21" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C21" t="s">
         <v>112</v>
@@ -19490,10 +19574,10 @@
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B22" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C22" t="s">
         <v>112</v>
@@ -19501,10 +19585,10 @@
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B23" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="C23" t="s">
         <v>112</v>
@@ -19512,10 +19596,10 @@
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B24" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C24" t="s">
         <v>112</v>
@@ -19523,10 +19607,10 @@
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B25" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C25" t="s">
         <v>112</v>
@@ -19534,10 +19618,10 @@
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B26" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C26" t="s">
         <v>112</v>
@@ -19545,10 +19629,10 @@
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B27" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C27" t="s">
         <v>112</v>
@@ -19556,21 +19640,21 @@
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B28" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C28" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B29" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C29" t="s">
         <v>112</v>
@@ -19578,10 +19662,10 @@
     </row>
     <row r="30" spans="1:3">
       <c r="A30" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B30" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C30" t="s">
         <v>112</v>
@@ -19589,10 +19673,10 @@
     </row>
     <row r="31" spans="1:3">
       <c r="A31" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B31" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C31" t="s">
         <v>112</v>
@@ -19600,10 +19684,10 @@
     </row>
     <row r="32" spans="1:3">
       <c r="A32" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B32" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C32" t="s">
         <v>112</v>
@@ -19611,21 +19695,21 @@
     </row>
     <row r="33" spans="1:3">
       <c r="A33" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B33" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C33" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="34" spans="1:3">
       <c r="A34" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B34" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C34" t="s">
         <v>112</v>
@@ -19633,10 +19717,10 @@
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B35" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C35" t="s">
         <v>112</v>
@@ -19644,10 +19728,10 @@
     </row>
     <row r="36" spans="1:3">
       <c r="A36" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B36" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C36" t="s">
         <v>112</v>
@@ -19655,13 +19739,13 @@
     </row>
     <row r="37" spans="1:3">
       <c r="A37" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B37" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C37" t="s">
-        <v>180</v>
+        <v>112</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -19669,7 +19753,7 @@
         <v>181</v>
       </c>
       <c r="B38" t="s">
-        <v>182</v>
+        <v>145</v>
       </c>
       <c r="C38" t="s">
         <v>112</v>
@@ -19677,10 +19761,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
+        <v>182</v>
+      </c>
+      <c r="B39" t="s">
         <v>183</v>
-      </c>
-      <c r="B39" t="s">
-        <v>184</v>
       </c>
       <c r="C39" t="s">
         <v>112</v>
@@ -19688,10 +19772,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
+        <v>184</v>
+      </c>
+      <c r="B40" t="s">
         <v>185</v>
-      </c>
-      <c r="B40" t="s">
-        <v>186</v>
       </c>
       <c r="C40" t="s">
         <v>112</v>
@@ -19699,10 +19783,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
+        <v>186</v>
+      </c>
+      <c r="B41" t="s">
         <v>187</v>
-      </c>
-      <c r="B41" t="s">
-        <v>188</v>
       </c>
       <c r="C41" t="s">
         <v>112</v>
@@ -19710,10 +19794,10 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
+        <v>188</v>
+      </c>
+      <c r="B42" t="s">
         <v>189</v>
-      </c>
-      <c r="B42" t="s">
-        <v>190</v>
       </c>
       <c r="C42" t="s">
         <v>112</v>
@@ -19721,10 +19805,10 @@
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
+        <v>190</v>
+      </c>
+      <c r="B43" t="s">
         <v>191</v>
-      </c>
-      <c r="B43" t="s">
-        <v>192</v>
       </c>
       <c r="C43" t="s">
         <v>112</v>
@@ -19732,10 +19816,10 @@
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
+        <v>192</v>
+      </c>
+      <c r="B44" t="s">
         <v>193</v>
-      </c>
-      <c r="B44" t="s">
-        <v>194</v>
       </c>
       <c r="C44" t="s">
         <v>112</v>
@@ -19743,10 +19827,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
+        <v>194</v>
+      </c>
+      <c r="B45" t="s">
         <v>195</v>
-      </c>
-      <c r="B45" t="s">
-        <v>196</v>
       </c>
       <c r="C45" t="s">
         <v>112</v>
@@ -19754,13 +19838,13 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
+        <v>196</v>
+      </c>
+      <c r="B46" t="s">
         <v>197</v>
       </c>
-      <c r="B46" t="s">
+      <c r="C46" t="s">
         <v>198</v>
-      </c>
-      <c r="C46" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="47" spans="1:3">
@@ -19776,10 +19860,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
+        <v>47</v>
+      </c>
+      <c r="B48" t="s">
         <v>201</v>
-      </c>
-      <c r="B48" t="s">
-        <v>202</v>
       </c>
       <c r="C48" t="s">
         <v>109</v>
@@ -19787,10 +19871,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
+        <v>202</v>
+      </c>
+      <c r="B49" t="s">
         <v>203</v>
-      </c>
-      <c r="B49" t="s">
-        <v>204</v>
       </c>
       <c r="C49" t="s">
         <v>112</v>
@@ -19798,10 +19882,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
+        <v>204</v>
+      </c>
+      <c r="B50" t="s">
         <v>205</v>
-      </c>
-      <c r="B50" t="s">
-        <v>206</v>
       </c>
       <c r="C50" t="s">
         <v>112</v>
@@ -19809,10 +19893,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
+        <v>206</v>
+      </c>
+      <c r="B51" t="s">
         <v>207</v>
-      </c>
-      <c r="B51" t="s">
-        <v>208</v>
       </c>
       <c r="C51" t="s">
         <v>112</v>
@@ -19820,10 +19904,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
+        <v>208</v>
+      </c>
+      <c r="B52" t="s">
         <v>209</v>
-      </c>
-      <c r="B52" t="s">
-        <v>210</v>
       </c>
       <c r="C52" t="s">
         <v>112</v>
@@ -19831,10 +19915,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
+        <v>210</v>
+      </c>
+      <c r="B53" t="s">
         <v>211</v>
-      </c>
-      <c r="B53" t="s">
-        <v>212</v>
       </c>
       <c r="C53" t="s">
         <v>112</v>
@@ -19842,10 +19926,10 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
+        <v>212</v>
+      </c>
+      <c r="B54" t="s">
         <v>213</v>
-      </c>
-      <c r="B54" t="s">
-        <v>214</v>
       </c>
       <c r="C54" t="s">
         <v>112</v>
@@ -19853,10 +19937,10 @@
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B55" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="C55" t="s">
         <v>112</v>
@@ -19864,10 +19948,10 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B56" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C56" t="s">
         <v>112</v>
@@ -19875,21 +19959,21 @@
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B57" t="s">
-        <v>140</v>
+        <v>218</v>
       </c>
       <c r="C57" t="s">
-        <v>112</v>
+        <v>198</v>
       </c>
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
+        <v>219</v>
+      </c>
+      <c r="B58" t="s">
         <v>220</v>
-      </c>
-      <c r="B58" t="s">
-        <v>221</v>
       </c>
       <c r="C58" t="s">
         <v>112</v>
@@ -19897,10 +19981,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59" t="s">
+        <v>221</v>
+      </c>
+      <c r="B59" t="s">
         <v>222</v>
-      </c>
-      <c r="B59" t="s">
-        <v>223</v>
       </c>
       <c r="C59" t="s">
         <v>112</v>
@@ -19908,21 +19992,21 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60" t="s">
+        <v>223</v>
+      </c>
+      <c r="B60" t="s">
         <v>224</v>
       </c>
-      <c r="B60" t="s">
-        <v>225</v>
-      </c>
       <c r="C60" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="61" spans="1:3">
       <c r="A61" t="s">
+        <v>225</v>
+      </c>
+      <c r="B61" t="s">
         <v>226</v>
-      </c>
-      <c r="B61" t="s">
-        <v>227</v>
       </c>
       <c r="C61" t="s">
         <v>112</v>
@@ -19930,13 +20014,178 @@
     </row>
     <row r="62" spans="1:3">
       <c r="A62" t="s">
+        <v>227</v>
+      </c>
+      <c r="B62" t="s">
         <v>228</v>
       </c>
-      <c r="B62" t="s">
+      <c r="C62" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3">
+      <c r="A63" t="s">
         <v>229</v>
       </c>
-      <c r="C62" t="s">
-        <v>180</v>
+      <c r="B63" t="s">
+        <v>230</v>
+      </c>
+      <c r="C63" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64" t="s">
+        <v>231</v>
+      </c>
+      <c r="B64" t="s">
+        <v>232</v>
+      </c>
+      <c r="C64" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3">
+      <c r="A65" t="s">
+        <v>233</v>
+      </c>
+      <c r="B65" t="s">
+        <v>234</v>
+      </c>
+      <c r="C65" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66" t="s">
+        <v>235</v>
+      </c>
+      <c r="B66" t="s">
+        <v>236</v>
+      </c>
+      <c r="C66" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67" t="s">
+        <v>237</v>
+      </c>
+      <c r="B67" t="s">
+        <v>238</v>
+      </c>
+      <c r="C67" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3">
+      <c r="A68" t="s">
+        <v>239</v>
+      </c>
+      <c r="B68" t="s">
+        <v>240</v>
+      </c>
+      <c r="C68" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3">
+      <c r="A69" t="s">
+        <v>241</v>
+      </c>
+      <c r="B69" t="s">
+        <v>140</v>
+      </c>
+      <c r="C69" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3">
+      <c r="A70" t="s">
+        <v>242</v>
+      </c>
+      <c r="B70" t="s">
+        <v>243</v>
+      </c>
+      <c r="C70" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3">
+      <c r="A71" t="s">
+        <v>244</v>
+      </c>
+      <c r="B71" t="s">
+        <v>245</v>
+      </c>
+      <c r="C71" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3">
+      <c r="A72" t="s">
+        <v>246</v>
+      </c>
+      <c r="B72" t="s">
+        <v>247</v>
+      </c>
+      <c r="C72" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3">
+      <c r="A73" t="s">
+        <v>248</v>
+      </c>
+      <c r="B73" t="s">
+        <v>249</v>
+      </c>
+      <c r="C73" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
+      <c r="A74" t="s">
+        <v>250</v>
+      </c>
+      <c r="B74" t="s">
+        <v>251</v>
+      </c>
+      <c r="C74" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
+      <c r="A75" t="s">
+        <v>252</v>
+      </c>
+      <c r="B75" t="s">
+        <v>253</v>
+      </c>
+      <c r="C75" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
+      <c r="A76" t="s">
+        <v>254</v>
+      </c>
+      <c r="B76" t="s">
+        <v>255</v>
+      </c>
+      <c r="C76" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
+      <c r="A77" t="s">
+        <v>256</v>
+      </c>
+      <c r="B77" t="s">
+        <v>257</v>
+      </c>
+      <c r="C77" t="s">
+        <v>112</v>
       </c>
     </row>
   </sheetData>

--- a/03_Group_comparisons/Proteome/05_Classification/03_Modules/c_data/module_classification_all_inputs.xlsx
+++ b/03_Group_comparisons/Proteome/05_Classification/03_Modules/c_data/module_classification_all_inputs.xlsx
@@ -315,31 +315,31 @@
     <t>03_Group_comparisons/Proteome/05_Classification/03_Modules/T1/c_data/module_classification.xlsx</t>
   </si>
   <si>
-    <t>7dcc6aad3d9589279a7edd748b8e30dd</t>
+    <t>26a7d057eaedf53a12592d34a441b09e</t>
   </si>
   <si>
     <t>03_Group_comparisons/Proteome/05_Classification/03_Modules/T2/c_data/module_classification.xlsx</t>
   </si>
   <si>
-    <t>4a846b61169b71c1d54ac4673726b5f7</t>
+    <t>2f0c5729f19d0020ba252e7b892415a0</t>
   </si>
   <si>
     <t>03_Group_comparisons/Proteome/05_Classification/03_Modules/T3/c_data/module_classification.xlsx</t>
   </si>
   <si>
-    <t>f97d3d53ea3e70223c5f0628b7cdb2c1</t>
+    <t>ca5aa4c2af626486bf01517932285615</t>
   </si>
   <si>
     <t>03_Group_comparisons/Proteome/05_Classification/03_Modules/training/c_data/module_classification.xlsx</t>
   </si>
   <si>
-    <t>6598fbc28466dfc782f2a0c55d7a6953</t>
+    <t>902afcf540f4dabbf54040d6735b678f</t>
   </si>
   <si>
     <t>03_Group_comparisons/Proteome/05_Classification/03_Modules/acute/c_data/module_classification.xlsx</t>
   </si>
   <si>
-    <t>78e870bed98446380fe7c25a0518072d</t>
+    <t>f3e1085cabf066c68bb3479745ca10ef</t>
   </si>
   <si>
     <t>BiocGenerics</t>
